--- a/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>1 公尺等於幾公分？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>8 cm³</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>100 cm</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>0.01cm</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>×100</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>1 公升等於幾毫升？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>1000 mL</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>可讀更小刻度、更精密</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>平均接近真值但分散</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>用細針壓入或加重物並扣除</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>1 mL 等於幾立方公分？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0.01cm</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1 cm³</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>體積換算</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>測量不規則固體體積用什麼方法？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>排水法</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>細長</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>碼錶</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>長×寬×高</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>排開水體積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>讀量筒時視線要對準？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>碼錶</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>凹液面最低處</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>公厘(mm)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>平視避免視差</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>比公分更小的長度單位是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>公厘(mm)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>隨機誤差</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>碼錶</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>1cm=10mm</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>規則長方體體積公式？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>長×寬×高</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>公尺m</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>V=lwh</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>測時間常用的工具是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>碼錶</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>系統誤差</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>長×寬×高</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>隨機誤差</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>計時</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>長度的SI單位是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>碼錶</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>公尺m</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>公厘(mm)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>1公分等於幾公厘？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>10 mm</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1000 L</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>0.75 L</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>×10</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>石頭放入量筒水面由40升到55mL，石頭體積？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>15 cm³</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>0.01cm</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>8 cm³</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1 cm³</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>55−40</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>2.5 m 等於幾 mm？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>2500 mm</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>用細針壓入或加重物並扣除</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>1000 mL</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>多次測量取平均</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>最小刻度0.1cm的尺量得長度應估到？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>15 cm³</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0.01cm</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>下一位</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>偏一致方向的誤差屬於？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>系統誤差</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>偏大</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>方向固定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>每次忽大忽小的誤差屬於？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>隨機誤差</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>細長</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>公尺m</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>凹液面最低處</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>偶然性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>降低隨機誤差最有效方法？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1000 mL</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>多次測量取平均</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>1200 mL</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>2500 mm</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>抵消偶然</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>邊長2cm正方體體積？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1 cm³</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>15 cm³</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>8 cm³</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>2³</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>750 mL 等於幾公升？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>0.75 L</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>1000 L</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>÷1000</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>邊長3cm正方體體積？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>8 cm³</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>27 cm³</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0.01cm</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>15 cm³</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>3³</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>1.2 L 等於幾 mL？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>用細針壓入或加重物並扣除</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2500 mm</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>1200 mL</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>可讀更小刻度、更精密</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上1-2 長度、體積與時間的測量　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>用排水法時物體會浮起，怎麼辦？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>可讀更小刻度、更精密</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1200 mL</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>量多張除以張數</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>用細針壓入或加重物並扣除</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>確保完全沒入</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>游標卡尺比直尺好在哪？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>可讀更小刻度、更精密</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>平均接近真值但分散</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>1200 mL</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>2500 mm</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>精密度較高</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>系統誤差能靠多次平均消除嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>長×寬×高</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>系統誤差</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>需校正工具</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>量筒選細長或粗矮較精確？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>碼錶</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>細長</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>系統誤差</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>刻度較密</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>某尺實際偏短，測值偏大或小？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>偏大</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>公尺m</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>系統誤差</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>系統誤差</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>3.20 cm 有幾位有效數字？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>27 cm³</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>10 mm</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>末0有效</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>1 m³ 等於幾公升？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>1000 L</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>8 cm³</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>1m³=1000L</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>準確但不精密指什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>量多張除以張數</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1200 mL</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>多次測量取平均</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>平均接近真值但分散</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>準確≠精密</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>測一張紙厚度較準的方法？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>多次測量取平均</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1000 mL</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>量多張除以張數</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>平均接近真值但分散</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>估測</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>量筒讀數在40與41間估讀40.5合理嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>合理</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>長×寬×高</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>細長</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>凹液面最低處</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>估到下一位</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>石頭放入量筒水面由40升到55mL，石頭體積？</t>
+          <t>石頭放入量筒，水面由40mL升高到55mL，石頭體積？</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>1 cm³</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>8 cm³</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>0.01cm</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>8 cm³</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1 cm³</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">

--- a/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>×100</t>
+          <t>×100：1公尺等於100公分，公尺換算公分要乘以100</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公升等於1000毫升，公升換算毫升要乘以1000</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>體積換算</t>
+          <t>體積換算：1毫升剛好等於1立方公分，這是常用的體積換算關係</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>排開水體積</t>
+          <t>排開水體積：把不規則物體放入水中，量出上升的水量，就等於物體排開的體積，這種方法叫排水法</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>平視避免視差</t>
+          <t>平視避免視差：水面呈凹形，視線要與凹液面最低處保持水平，才能避免因視角造成的讀數誤差</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>1cm=10mm</t>
+          <t>1cm=10mm：比公分更小的常用長度單位是公厘(毫米)，1公分等於10公厘</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>V=lwh</t>
+          <t>V=lwh：長方體的體積等於長乘以寬再乘以高</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>計時</t>
+          <t>計時：碼錶能精準測量經過的時間，是實驗中常用的計時工具</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI：國際單位制(SI)規定長度的基本單位是公尺，符號寫作m</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>×10</t>
+          <t>×10：1公分等於10公厘，公分換算公厘要乘以10</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>55−40</t>
+          <t>55−40：石頭排開的水量=上升後水量−原本水量，55減去40等於15立方公分</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公尺等於1000公厘，2.5乘以1000等於2500公厘</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>下一位</t>
+          <t>下一位：讀數要在最小刻度之下再估讀一位，最小刻度是0.1cm，所以要估到0.01cm這一位</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>方向固定</t>
+          <t>方向固定：每次測量都朝同一個方向偏差(例如都偏大或都偏小)，這種誤差稱為系統誤差，通常來自儀器本身的問題</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>偶然性</t>
+          <t>偶然性：每次測量誤差方向和大小都不固定、忽大忽小，這種偶然發生的誤差稱為隨機誤差</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>抵消偶然</t>
+          <t>抵消偶然：多次測量後取平均值，可以讓忽大忽小的隨機誤差互相抵消，使結果更接近真實值</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2³</t>
+          <t>2³：正方體體積=邊長×邊長×邊長，2×2×2=8立方公分</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>÷1000</t>
+          <t>÷1000：1公升等於1000毫升，750除以1000等於0.75公升</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>3³</t>
+          <t>3³：正方體體積=邊長×邊長×邊長，3×3×3=27立方公分</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公升等於1000毫升，1.2乘以1000等於1200毫升</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>確保完全沒入</t>
+          <t>確保完全沒入：物體會浮起代表沒有完全沒入水中，測出的體積不準確，可以用細針把它壓入水中，或加上不吸水的重物幫忙下沉，最後再扣除重物本身的體積</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>精密度較高</t>
+          <t>精密度較高：游標卡尺利用特殊刻度設計，可以讀到比一般直尺更小的刻度，測量結果比較精密</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>需校正工具</t>
+          <t>需校正工具：系統誤差每次都朝固定方向偏差，就算重複測量取平均也無法消除，必須重新校正測量工具才能解決</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>刻度較密</t>
+          <t>刻度較密：相同容量下，細長型量筒的刻度間距比粗矮型更寬、劃分更細密，讀數會比較精確</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>系統誤差</t>
+          <t>系統誤差：如果尺本身的實際長度比標示的短，用它量出來的數值會比真實長度偏大，這是一種系統誤差</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>末0有效</t>
+          <t>末0有效：3、2、0這三個數字都是測量得到的結果，末位的0也算有效數字，所以共有3位</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>1m³=1000L</t>
+          <t>1m³=1000L：1立方公尺等於1000公升，這是常用的體積單位換算關係</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>準確≠精密</t>
+          <t>準確≠精密：準確是指多次測量的平均值很接近真實值，精密則是指每次測量結果彼此接近、分散程度小；「準確但不精密」代表平均值雖然對，但每次測量的數值差異較大</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>估測</t>
+          <t>估測：直接測一張紙誤差太大，量很多張疊在一起的總厚度再除以張數，可以縮小測量誤差</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>估到下一位</t>
+          <t>估到下一位：讀取量筒刻度時，除了讀到最小刻度，還要再往下估讀一位，40.5就是在最小刻度之間合理估讀的結果</t>
         </is>
       </c>
     </row>
